--- a/XlsxSharp.Tests/Resource/Examples/ConditionalFormatting/CFEqualsString.xlsx
+++ b/XlsxSharp.Tests/Resource/Examples/ConditionalFormatting/CFEqualsString.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:workbookPr codeName="ThisWorkbook"/>
-  <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="0"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" r:id="rId2"/>
-  </x:sheets>
-  <x:definedNames/>
-  <x:calcPr calcId="125725"/>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView firstSheet="0" activeTab="0"/>
+  </bookViews>
+  <sheets>
+    <sheet r:id="rId1" name="Sheet1" sheetId="1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="125725"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t>Hello</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hellos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hell</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Holl</x:t>
-  </x:si>
-</x:sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <si>
+    <t>Hello</t>
+  </si>
+  <si>
+    <t>Hellos</t>
+  </si>
+  <si>
+    <t>Hell</t>
+  </si>
+  <si>
+    <t>Holl</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -371,43 +371,43 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:A4"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData>
-    <x:row r="1" spans="1:1">
-      <x:c r="A1" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:1">
-      <x:c r="A2" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:1">
-      <x:c r="A3" s="0" t="s">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:1">
-      <x:c r="A4" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:conditionalFormatting sqref="A1:A4">
-    <x:cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <x:formula>"Hell"</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:A4">
+    <cfRule type="cellIs" priority="1" dxfId="0" operator="equal">
+      <formula>"Hell"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>